--- a/Table/Datas/CharacterStatusData.xlsx
+++ b/Table/Datas/CharacterStatusData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Unreal\ProjectH\Table\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741E987B-D467-489A-A879-C1CD515B7AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6332FECA-F1B9-4CBB-8F38-BACD8F16C45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="14">
   <si>
     <t>!Field</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -77,6 +77,10 @@
   <si>
     <t>SP</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Threat</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -446,16 +450,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:I8"/>
+  <dimension ref="A2:J8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="7.375" customWidth="1"/>
     <col min="4" max="4" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -483,8 +487,11 @@
       <c r="I2" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -512,8 +519,11 @@
       <c r="I3" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="J3" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -541,8 +551,11 @@
       <c r="I4" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="J4" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -570,8 +583,11 @@
       <c r="I5" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="J5" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>101</v>
       </c>
@@ -599,8 +615,11 @@
       <c r="I6" s="3">
         <v>100</v>
       </c>
+      <c r="J6" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>102</v>
       </c>
@@ -628,8 +647,11 @@
       <c r="I7" s="3">
         <v>101</v>
       </c>
+      <c r="J7" s="3">
+        <v>101</v>
+      </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -639,6 +661,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
